--- a/data/nzd0304/nzd0304.xlsx
+++ b/data/nzd0304/nzd0304.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K750"/>
+  <dimension ref="A1:K753"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29694,6 +29694,123 @@
         <v>350.87</v>
       </c>
       <c r="K750" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-13 22:00:04+00:00</t>
+        </is>
+      </c>
+      <c r="B751" t="n">
+        <v>354.98</v>
+      </c>
+      <c r="C751" t="n">
+        <v>367.39</v>
+      </c>
+      <c r="D751" t="n">
+        <v>364.02</v>
+      </c>
+      <c r="E751" t="n">
+        <v>359.64</v>
+      </c>
+      <c r="F751" t="n">
+        <v>348.32</v>
+      </c>
+      <c r="G751" t="n">
+        <v>340.07</v>
+      </c>
+      <c r="H751" t="n">
+        <v>340.67</v>
+      </c>
+      <c r="I751" t="n">
+        <v>343.1</v>
+      </c>
+      <c r="J751" t="n">
+        <v>350.18</v>
+      </c>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-14 21:54:04+00:00</t>
+        </is>
+      </c>
+      <c r="B752" t="n">
+        <v>355.02</v>
+      </c>
+      <c r="C752" t="n">
+        <v>366.9</v>
+      </c>
+      <c r="D752" t="n">
+        <v>363.46</v>
+      </c>
+      <c r="E752" t="n">
+        <v>359.06</v>
+      </c>
+      <c r="F752" t="n">
+        <v>347.78</v>
+      </c>
+      <c r="G752" t="n">
+        <v>340.11</v>
+      </c>
+      <c r="H752" t="n">
+        <v>340.65</v>
+      </c>
+      <c r="I752" t="n">
+        <v>343.26</v>
+      </c>
+      <c r="J752" t="n">
+        <v>350.06</v>
+      </c>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-21 22:00:20+00:00</t>
+        </is>
+      </c>
+      <c r="B753" t="n">
+        <v>354.86</v>
+      </c>
+      <c r="C753" t="n">
+        <v>366.75</v>
+      </c>
+      <c r="D753" t="n">
+        <v>363.09</v>
+      </c>
+      <c r="E753" t="n">
+        <v>358.66</v>
+      </c>
+      <c r="F753" t="n">
+        <v>347.66</v>
+      </c>
+      <c r="G753" t="n">
+        <v>340.21</v>
+      </c>
+      <c r="H753" t="n">
+        <v>340.42</v>
+      </c>
+      <c r="I753" t="n">
+        <v>343.02</v>
+      </c>
+      <c r="J753" t="n">
+        <v>349.7</v>
+      </c>
+      <c r="K753" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29710,7 +29827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B758"/>
+  <dimension ref="A1:B761"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37293,6 +37410,36 @@
       </c>
       <c r="B758" t="n">
         <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>2026-07-13 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B759" t="n">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>2026-07-14 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B760" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>2026-07-21 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B761" t="n">
+        <v>0.34</v>
       </c>
     </row>
   </sheetData>
@@ -37461,28 +37608,28 @@
         <v>0.0428</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7317774661471096</v>
+        <v>-0.7337267309311727</v>
       </c>
       <c r="J2" t="n">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="K2" t="n">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5387830194823473</v>
+        <v>0.5422166776828503</v>
       </c>
       <c r="M2" t="n">
-        <v>4.133445155332894</v>
+        <v>4.125070627311918</v>
       </c>
       <c r="N2" t="n">
-        <v>25.23951204049981</v>
+        <v>25.16112682409939</v>
       </c>
       <c r="O2" t="n">
-        <v>5.023894111195002</v>
+        <v>5.016086803884019</v>
       </c>
       <c r="P2" t="n">
-        <v>377.0527649445525</v>
+        <v>377.0736403155987</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37539,28 +37686,28 @@
         <v>0.0458</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6275741842152786</v>
+        <v>-0.6279904737849062</v>
       </c>
       <c r="J3" t="n">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="K3" t="n">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="L3" t="n">
-        <v>0.423364386617116</v>
+        <v>0.4259722417858313</v>
       </c>
       <c r="M3" t="n">
-        <v>4.29849483788151</v>
+        <v>4.282973142075617</v>
       </c>
       <c r="N3" t="n">
-        <v>29.53580290231836</v>
+        <v>29.41927832687452</v>
       </c>
       <c r="O3" t="n">
-        <v>5.434685170487649</v>
+        <v>5.423954122858574</v>
       </c>
       <c r="P3" t="n">
-        <v>384.4293598218932</v>
+        <v>384.4338186667613</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37617,28 +37764,28 @@
         <v>0.0356</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7894870234394959</v>
+        <v>-0.7900478328732345</v>
       </c>
       <c r="J4" t="n">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="K4" t="n">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3971042315989464</v>
+        <v>0.3996845130500269</v>
       </c>
       <c r="M4" t="n">
-        <v>5.627381670257527</v>
+        <v>5.607661991863495</v>
       </c>
       <c r="N4" t="n">
-        <v>52.1025782776925</v>
+        <v>51.89712601674246</v>
       </c>
       <c r="O4" t="n">
-        <v>7.218211570582598</v>
+        <v>7.203965992197802</v>
       </c>
       <c r="P4" t="n">
-        <v>385.4840829980301</v>
+        <v>385.4900899554842</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37695,28 +37842,28 @@
         <v>0.0368</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5490356800943019</v>
+        <v>-0.550052136831396</v>
       </c>
       <c r="J5" t="n">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="K5" t="n">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2717186196505713</v>
+        <v>0.2742868784806133</v>
       </c>
       <c r="M5" t="n">
-        <v>5.32303252982173</v>
+        <v>5.306420472370882</v>
       </c>
       <c r="N5" t="n">
-        <v>44.48488237838446</v>
+        <v>44.31410319184219</v>
       </c>
       <c r="O5" t="n">
-        <v>6.669698822164646</v>
+        <v>6.656883895024922</v>
       </c>
       <c r="P5" t="n">
-        <v>375.1526286604281</v>
+        <v>375.1635153390447</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37773,28 +37920,28 @@
         <v>0.0361</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.408193250837105</v>
+        <v>-0.4118016316146783</v>
       </c>
       <c r="J6" t="n">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="K6" t="n">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1792469675480244</v>
+        <v>0.1829787158824028</v>
       </c>
       <c r="M6" t="n">
-        <v>5.315856259231758</v>
+        <v>5.311319146438612</v>
       </c>
       <c r="N6" t="n">
-        <v>42.00720829987559</v>
+        <v>41.91632797459546</v>
       </c>
       <c r="O6" t="n">
-        <v>6.481296806957354</v>
+        <v>6.474282043176329</v>
       </c>
       <c r="P6" t="n">
-        <v>363.3250628389482</v>
+        <v>363.3637066285186</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37851,28 +37998,28 @@
         <v>0.0362</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3155918177682969</v>
+        <v>-0.3182938151712018</v>
       </c>
       <c r="J7" t="n">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="K7" t="n">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1075856827744305</v>
+        <v>0.1100582864794252</v>
       </c>
       <c r="M7" t="n">
-        <v>5.481779975435365</v>
+        <v>5.472761120833474</v>
       </c>
       <c r="N7" t="n">
-        <v>45.48780918747049</v>
+        <v>45.34918904227548</v>
       </c>
       <c r="O7" t="n">
-        <v>6.744465077933942</v>
+        <v>6.734180651146469</v>
       </c>
       <c r="P7" t="n">
-        <v>351.932225154236</v>
+        <v>351.9611613369169</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37929,28 +38076,28 @@
         <v>0.036</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2298820909560887</v>
+        <v>-0.2331527970027067</v>
       </c>
       <c r="J8" t="n">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="K8" t="n">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05459798532458338</v>
+        <v>0.05650738779157183</v>
       </c>
       <c r="M8" t="n">
-        <v>5.806140117373826</v>
+        <v>5.797947421748692</v>
       </c>
       <c r="N8" t="n">
-        <v>50.38272876032064</v>
+        <v>50.24453612276753</v>
       </c>
       <c r="O8" t="n">
-        <v>7.098079230349619</v>
+        <v>7.088338036716896</v>
       </c>
       <c r="P8" t="n">
-        <v>350.7658219243725</v>
+        <v>350.8008491404802</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -38007,28 +38154,28 @@
         <v>0.0354</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.204084050509701</v>
+        <v>-0.2073326489498756</v>
       </c>
       <c r="J9" t="n">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="K9" t="n">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04271517716072915</v>
+        <v>0.04437119050483684</v>
       </c>
       <c r="M9" t="n">
-        <v>5.84668561780264</v>
+        <v>5.83892075074832</v>
       </c>
       <c r="N9" t="n">
-        <v>51.3935472219848</v>
+        <v>51.25047022609581</v>
       </c>
       <c r="O9" t="n">
-        <v>7.168929293973041</v>
+        <v>7.158943373577961</v>
       </c>
       <c r="P9" t="n">
-        <v>352.5915145515539</v>
+        <v>352.6263048609828</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -38085,28 +38232,28 @@
         <v>0.0406</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1239846539155291</v>
+        <v>-0.1266225312698513</v>
       </c>
       <c r="J10" t="n">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="K10" t="n">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02182184838796319</v>
+        <v>0.02292429930947504</v>
       </c>
       <c r="M10" t="n">
-        <v>4.898074987916017</v>
+        <v>4.891311568219816</v>
       </c>
       <c r="N10" t="n">
-        <v>37.939691430906</v>
+        <v>37.82931119735653</v>
       </c>
       <c r="O10" t="n">
-        <v>6.159520389681813</v>
+        <v>6.150553730954354</v>
       </c>
       <c r="P10" t="n">
-        <v>356.5401352586745</v>
+        <v>356.5683856475162</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -38144,7 +38291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K750"/>
+  <dimension ref="A1:K753"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80897,6 +81044,177 @@
         </is>
       </c>
     </row>
+    <row r="751">
+      <c r="A751" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-13 22:00:04+00:00</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>-40.02175632667309,176.89118285278366</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>-40.02241797395299,176.89091025269997</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>-40.02301949558815,176.89047035226704</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>-40.023617163483365,176.89001974297904</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>-40.02418890396752,176.88949486068327</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>-40.024784088527895,176.88902654210352</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>-40.02541156735611,176.88865791796547</t>
+        </is>
+      </c>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>-40.0260452267384,176.88830920247116</t>
+        </is>
+      </c>
+      <c r="J751" t="inlineStr">
+        <is>
+          <t>-40.0266952162985,176.88801059039676</t>
+        </is>
+      </c>
+      <c r="K751" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-14 21:54:04+00:00</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>-40.02175647906875,176.89118327686387</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>-40.02241610710182,176.89090505766868</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>-40.023017362029876,176.8904644150426</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>-40.02361495371137,176.89001359366404</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>-40.024186915928475,176.88948909411346</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>-40.02478422983354,176.88902697265135</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t>-40.025411497095185,176.88865770247259</t>
+        </is>
+      </c>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>-40.02604578882855,176.88831092642909</t>
+        </is>
+      </c>
+      <c r="J752" t="inlineStr">
+        <is>
+          <t>-40.026694794729366,176.88800929741652</t>
+        </is>
+      </c>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-21 22:00:20+00:00</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>-40.021755869486135,176.89118158054302</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>-40.02241553561673,176.890903467353</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>-40.023015952357234,176.89046049223379</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>-40.0236134297305,176.89000935275735</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>-40.02418647414198,176.88948781265356</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>-40.024784583097706,176.889028049021</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>-40.02541068909454,176.88865522430456</t>
+        </is>
+      </c>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>-40.026044945693315,176.8883083404922</t>
+        </is>
+      </c>
+      <c r="J753" t="inlineStr">
+        <is>
+          <t>-40.02669353002188,176.88800541847598</t>
+        </is>
+      </c>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0304/nzd0304.xlsx
+++ b/data/nzd0304/nzd0304.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K753"/>
+  <dimension ref="A1:K758"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29811,6 +29811,201 @@
         <v>349.7</v>
       </c>
       <c r="K753" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:54:00+00:00</t>
+        </is>
+      </c>
+      <c r="B754" t="n">
+        <v>354.86</v>
+      </c>
+      <c r="C754" t="n">
+        <v>366.5</v>
+      </c>
+      <c r="D754" t="n">
+        <v>362.8</v>
+      </c>
+      <c r="E754" t="n">
+        <v>358.66</v>
+      </c>
+      <c r="F754" t="n">
+        <v>347.66</v>
+      </c>
+      <c r="G754" t="n">
+        <v>340.21</v>
+      </c>
+      <c r="H754" t="n">
+        <v>340.42</v>
+      </c>
+      <c r="I754" t="n">
+        <v>343.02</v>
+      </c>
+      <c r="J754" t="n">
+        <v>349.7</v>
+      </c>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:00:15+00:00</t>
+        </is>
+      </c>
+      <c r="B755" t="n">
+        <v>354.39</v>
+      </c>
+      <c r="C755" t="n">
+        <v>365.9</v>
+      </c>
+      <c r="D755" t="n">
+        <v>361.82</v>
+      </c>
+      <c r="E755" t="n">
+        <v>357.91</v>
+      </c>
+      <c r="F755" t="n">
+        <v>347.16</v>
+      </c>
+      <c r="G755" t="n">
+        <v>339.83</v>
+      </c>
+      <c r="H755" t="n">
+        <v>339.83</v>
+      </c>
+      <c r="I755" t="n">
+        <v>342.21</v>
+      </c>
+      <c r="J755" t="n">
+        <v>349.02</v>
+      </c>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:54:15+00:00</t>
+        </is>
+      </c>
+      <c r="B756" t="n">
+        <v>354.16</v>
+      </c>
+      <c r="C756" t="n">
+        <v>365.8</v>
+      </c>
+      <c r="D756" t="n">
+        <v>361.21</v>
+      </c>
+      <c r="E756" t="n">
+        <v>357.6</v>
+      </c>
+      <c r="F756" t="n">
+        <v>347.05</v>
+      </c>
+      <c r="G756" t="n">
+        <v>339.94</v>
+      </c>
+      <c r="H756" t="n">
+        <v>339.6</v>
+      </c>
+      <c r="I756" t="n">
+        <v>341.76</v>
+      </c>
+      <c r="J756" t="n">
+        <v>348.67</v>
+      </c>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-06 22:00:27+00:00</t>
+        </is>
+      </c>
+      <c r="B757" t="n">
+        <v>353.69</v>
+      </c>
+      <c r="C757" t="n">
+        <v>365.32</v>
+      </c>
+      <c r="D757" t="n">
+        <v>360.79</v>
+      </c>
+      <c r="E757" t="n">
+        <v>356.8</v>
+      </c>
+      <c r="F757" t="n">
+        <v>345.73</v>
+      </c>
+      <c r="G757" t="n">
+        <v>338.72</v>
+      </c>
+      <c r="H757" t="n">
+        <v>339.02</v>
+      </c>
+      <c r="I757" t="n">
+        <v>340.56</v>
+      </c>
+      <c r="J757" t="n">
+        <v>347.94</v>
+      </c>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-22 22:00:28+00:00</t>
+        </is>
+      </c>
+      <c r="B758" t="n">
+        <v>353.98</v>
+      </c>
+      <c r="C758" t="n">
+        <v>365.2</v>
+      </c>
+      <c r="D758" t="n">
+        <v>360.72</v>
+      </c>
+      <c r="E758" t="n">
+        <v>356.05</v>
+      </c>
+      <c r="F758" t="n">
+        <v>344.14</v>
+      </c>
+      <c r="G758" t="n">
+        <v>336.99</v>
+      </c>
+      <c r="H758" t="n">
+        <v>337.85</v>
+      </c>
+      <c r="I758" t="n">
+        <v>340.03</v>
+      </c>
+      <c r="J758" t="n">
+        <v>347.46</v>
+      </c>
+      <c r="K758" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29827,7 +30022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B761"/>
+  <dimension ref="A1:B766"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37440,6 +37635,56 @@
       </c>
       <c r="B761" t="n">
         <v>0.34</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B762" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B763" t="n">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B764" t="n">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>2026-08-06 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B765" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>2026-08-22 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B766" t="n">
+        <v>-0.11</v>
       </c>
     </row>
   </sheetData>
@@ -37608,28 +37853,28 @@
         <v>0.0428</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7337267309311727</v>
+        <v>-0.7378199110259106</v>
       </c>
       <c r="J2" t="n">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="K2" t="n">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5422166776828503</v>
+        <v>0.5481960944678317</v>
       </c>
       <c r="M2" t="n">
-        <v>4.125070627311918</v>
+        <v>4.114706919379015</v>
       </c>
       <c r="N2" t="n">
-        <v>25.16112682409939</v>
+        <v>25.05605347431465</v>
       </c>
       <c r="O2" t="n">
-        <v>5.016086803884019</v>
+        <v>5.005602208956945</v>
       </c>
       <c r="P2" t="n">
-        <v>377.0736403155987</v>
+        <v>377.1175665493117</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37686,28 +37931,28 @@
         <v>0.0458</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6279904737849062</v>
+        <v>-0.6303225940501614</v>
       </c>
       <c r="J3" t="n">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="K3" t="n">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4259722417858313</v>
+        <v>0.4313926765267475</v>
       </c>
       <c r="M3" t="n">
-        <v>4.282973142075617</v>
+        <v>4.263817706329132</v>
       </c>
       <c r="N3" t="n">
-        <v>29.41927832687452</v>
+        <v>29.24578695304755</v>
       </c>
       <c r="O3" t="n">
-        <v>5.423954122858574</v>
+        <v>5.407937402841083</v>
       </c>
       <c r="P3" t="n">
-        <v>384.4338186667613</v>
+        <v>384.4588501248764</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37764,28 +38009,28 @@
         <v>0.0356</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7900478328732345</v>
+        <v>-0.7936635479324823</v>
       </c>
       <c r="J4" t="n">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="K4" t="n">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3996845130500269</v>
+        <v>0.4053557074414128</v>
       </c>
       <c r="M4" t="n">
-        <v>5.607661991863495</v>
+        <v>5.588035907345652</v>
       </c>
       <c r="N4" t="n">
-        <v>51.89712601674246</v>
+        <v>51.60499167170021</v>
       </c>
       <c r="O4" t="n">
-        <v>7.203965992197802</v>
+        <v>7.18366143910612</v>
       </c>
       <c r="P4" t="n">
-        <v>385.4900899554842</v>
+        <v>385.5288985721637</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37842,28 +38087,28 @@
         <v>0.0368</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.550052136831396</v>
+        <v>-0.5539586015887661</v>
       </c>
       <c r="J5" t="n">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="K5" t="n">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2742868784806133</v>
+        <v>0.2799407524114796</v>
       </c>
       <c r="M5" t="n">
-        <v>5.306420472370882</v>
+        <v>5.28893268967947</v>
       </c>
       <c r="N5" t="n">
-        <v>44.31410319184219</v>
+        <v>44.08132182674814</v>
       </c>
       <c r="O5" t="n">
-        <v>6.656883895024922</v>
+        <v>6.639376614317653</v>
       </c>
       <c r="P5" t="n">
-        <v>375.1635153390447</v>
+        <v>375.2054481061157</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37920,28 +38165,28 @@
         <v>0.0361</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4118016316146783</v>
+        <v>-0.4197207473827231</v>
       </c>
       <c r="J6" t="n">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="K6" t="n">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1829787158824028</v>
+        <v>0.1902465066363729</v>
       </c>
       <c r="M6" t="n">
-        <v>5.311319146438612</v>
+        <v>5.313069453712861</v>
       </c>
       <c r="N6" t="n">
-        <v>41.91632797459546</v>
+        <v>41.87500732244487</v>
       </c>
       <c r="O6" t="n">
-        <v>6.474282043176329</v>
+        <v>6.471090118553819</v>
       </c>
       <c r="P6" t="n">
-        <v>363.3637066285186</v>
+        <v>363.4487038384688</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37998,28 +38243,28 @@
         <v>0.0362</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3182938151712018</v>
+        <v>-0.3239719357948792</v>
       </c>
       <c r="J7" t="n">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="K7" t="n">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1100582864794252</v>
+        <v>0.1148513515252665</v>
       </c>
       <c r="M7" t="n">
-        <v>5.472761120833474</v>
+        <v>5.463440218679454</v>
       </c>
       <c r="N7" t="n">
-        <v>45.34918904227548</v>
+        <v>45.17443855851598</v>
       </c>
       <c r="O7" t="n">
-        <v>6.734180651146469</v>
+        <v>6.721193239188707</v>
       </c>
       <c r="P7" t="n">
-        <v>351.9611613369169</v>
+        <v>352.022109974291</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -38076,28 +38321,28 @@
         <v>0.036</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2331527970027067</v>
+        <v>-0.2400793700622976</v>
       </c>
       <c r="J8" t="n">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="K8" t="n">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05650738779157183</v>
+        <v>0.06038229629257796</v>
       </c>
       <c r="M8" t="n">
-        <v>5.797947421748692</v>
+        <v>5.791062117530815</v>
       </c>
       <c r="N8" t="n">
-        <v>50.24453612276753</v>
+        <v>50.08978104756266</v>
       </c>
       <c r="O8" t="n">
-        <v>7.088338036716896</v>
+        <v>7.07741344331124</v>
       </c>
       <c r="P8" t="n">
-        <v>350.8008491404802</v>
+        <v>350.8751893525933</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -38154,28 +38399,28 @@
         <v>0.0354</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2073326489498756</v>
+        <v>-0.2147310746671697</v>
       </c>
       <c r="J9" t="n">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="K9" t="n">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04437119050483684</v>
+        <v>0.04796063997340183</v>
       </c>
       <c r="M9" t="n">
-        <v>5.83892075074832</v>
+        <v>5.835622967773677</v>
       </c>
       <c r="N9" t="n">
-        <v>51.25047022609581</v>
+        <v>51.11608821240925</v>
       </c>
       <c r="O9" t="n">
-        <v>7.158943373577961</v>
+        <v>7.149551609185659</v>
       </c>
       <c r="P9" t="n">
-        <v>352.6263048609828</v>
+        <v>352.7057107751859</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -38232,28 +38477,28 @@
         <v>0.0406</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1266225312698513</v>
+        <v>-0.1327826133179608</v>
       </c>
       <c r="J10" t="n">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="K10" t="n">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02292429930947504</v>
+        <v>0.0254401943221747</v>
       </c>
       <c r="M10" t="n">
-        <v>4.891311568219816</v>
+        <v>4.88879497796062</v>
       </c>
       <c r="N10" t="n">
-        <v>37.82931119735653</v>
+        <v>37.71971272146236</v>
       </c>
       <c r="O10" t="n">
-        <v>6.150553730954354</v>
+        <v>6.141637625378297</v>
       </c>
       <c r="P10" t="n">
-        <v>356.5683856475162</v>
+        <v>356.6344989701932</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -38291,7 +38536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K753"/>
+  <dimension ref="A1:K758"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81215,6 +81460,291 @@
         </is>
       </c>
     </row>
+    <row r="754">
+      <c r="A754" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-22 21:54:00+00:00</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>-40.021755869486135,176.89118158054302</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>-40.0224145831415,176.89090081682698</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>-40.02301484747861,176.89045741759995</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>-40.0236134297305,176.89000935275735</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>-40.02418647414198,176.88948781265356</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>-40.024784583097706,176.889028049021</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr">
+        <is>
+          <t>-40.02541068909454,176.88865522430456</t>
+        </is>
+      </c>
+      <c r="I754" t="inlineStr">
+        <is>
+          <t>-40.026044945693315,176.8883083404922</t>
+        </is>
+      </c>
+      <c r="J754" t="inlineStr">
+        <is>
+          <t>-40.02669353002188,176.88800541847598</t>
+        </is>
+      </c>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:00:15+00:00</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>-40.02175407883709,176.89117659760066</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>-40.02241229720071,176.89089445556482</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>-40.02301111375016,176.89044702745875</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>-40.023610572265895,176.89000140105784</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>-40.024184633364754,176.8894824732374</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>-40.02478324069386,176.88902395881647</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>-40.025408616396994,176.88864886726503</t>
+        </is>
+      </c>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>-40.02604210011145,176.88829961295556</t>
+        </is>
+      </c>
+      <c r="J755" t="inlineStr">
+        <is>
+          <t>-40.026691141129604,176.8879980915886</t>
+        </is>
+      </c>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-30 21:54:15+00:00</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>-40.02175320256195,176.89117415913958</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>-40.022411916210544,176.89089339535448</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>-40.0230087896942,176.89044056012648</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>-40.02360939118036,176.88999811435556</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>-40.02418422839373,176.8894812985659</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>-40.02478362928447,176.88902514282304</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t>-40.02540780839617,176.88864638909718</t>
+        </is>
+      </c>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>-40.026040519232325,176.8882947643244</t>
+        </is>
+      </c>
+      <c r="J756" t="inlineStr">
+        <is>
+          <t>-40.0266899115525,176.88799432039676</t>
+        </is>
+      </c>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-06 22:00:27+00:00</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>-40.02175141191255,176.8911691761976</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>-40.022410087457594,176.8908883063451</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>-40.0230071895243,176.89043610720947</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>-40.02360634321723,176.8899896325437</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>-40.024179368740455,176.8894672025087</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>-40.024779319460684,176.88901201111466</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t>-40.025405770828584,176.8886401398046</t>
+        </is>
+      </c>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>-40.02603630355363,176.88828183464233</t>
+        </is>
+      </c>
+      <c r="J757" t="inlineStr">
+        <is>
+          <t>-40.02668734700556,176.8879864547685</t>
+        </is>
+      </c>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-22 22:00:28+00:00</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>-40.02175251678135,176.8911722507788</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>-40.022409630269316,176.89088703409277</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>-40.023006922829296,176.89043536505665</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>-40.023603485751195,176.88998168084572</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>-40.02417351506479,176.88945022316966</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>-40.024773207986556,176.88899338992437</t>
+        </is>
+      </c>
+      <c r="H758" t="inlineStr">
+        <is>
+          <t>-40.025401660561855,176.88862753347408</t>
+        </is>
+      </c>
+      <c r="I758" t="inlineStr">
+        <is>
+          <t>-40.02603444162838,176.88827612403324</t>
+        </is>
+      </c>
+      <c r="J758" t="inlineStr">
+        <is>
+          <t>-40.026685660727814,176.88798128284884</t>
+        </is>
+      </c>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0304/nzd0304.xlsx
+++ b/data/nzd0304/nzd0304.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K758"/>
+  <dimension ref="A1:K765"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30006,6 +30006,279 @@
         <v>347.46</v>
       </c>
       <c r="K758" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:54:15+00:00</t>
+        </is>
+      </c>
+      <c r="B759" t="n">
+        <v>354.26</v>
+      </c>
+      <c r="C759" t="n">
+        <v>365.55</v>
+      </c>
+      <c r="D759" t="n">
+        <v>360.99</v>
+      </c>
+      <c r="E759" t="n">
+        <v>356.09</v>
+      </c>
+      <c r="F759" t="n">
+        <v>343.93</v>
+      </c>
+      <c r="G759" t="n">
+        <v>336.46</v>
+      </c>
+      <c r="H759" t="n">
+        <v>337.38</v>
+      </c>
+      <c r="I759" t="n">
+        <v>339.71</v>
+      </c>
+      <c r="J759" t="n">
+        <v>347.41</v>
+      </c>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-30 22:00:28+00:00</t>
+        </is>
+      </c>
+      <c r="B760" t="n">
+        <v>354.28</v>
+      </c>
+      <c r="C760" t="n">
+        <v>365.19</v>
+      </c>
+      <c r="D760" t="n">
+        <v>360.44</v>
+      </c>
+      <c r="E760" t="n">
+        <v>354.44</v>
+      </c>
+      <c r="F760" t="n">
+        <v>342.21</v>
+      </c>
+      <c r="G760" t="n">
+        <v>334.61</v>
+      </c>
+      <c r="H760" t="n">
+        <v>335.69</v>
+      </c>
+      <c r="I760" t="n">
+        <v>338.2</v>
+      </c>
+      <c r="J760" t="n">
+        <v>346.35</v>
+      </c>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-31 21:54:23+00:00</t>
+        </is>
+      </c>
+      <c r="B761" t="n">
+        <v>354.55</v>
+      </c>
+      <c r="C761" t="n">
+        <v>365.53</v>
+      </c>
+      <c r="D761" t="n">
+        <v>360.55</v>
+      </c>
+      <c r="E761" t="n">
+        <v>354.39</v>
+      </c>
+      <c r="F761" t="n">
+        <v>342.24</v>
+      </c>
+      <c r="G761" t="n">
+        <v>334.39</v>
+      </c>
+      <c r="H761" t="n">
+        <v>335.5</v>
+      </c>
+      <c r="I761" t="n">
+        <v>337.73</v>
+      </c>
+      <c r="J761" t="n">
+        <v>346.19</v>
+      </c>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-08 21:54:17+00:00</t>
+        </is>
+      </c>
+      <c r="B762" t="n">
+        <v>355.14</v>
+      </c>
+      <c r="C762" t="n">
+        <v>365.89</v>
+      </c>
+      <c r="D762" t="n">
+        <v>360.44</v>
+      </c>
+      <c r="E762" t="n">
+        <v>353.99</v>
+      </c>
+      <c r="F762" t="n">
+        <v>341.77</v>
+      </c>
+      <c r="G762" t="n">
+        <v>333.63</v>
+      </c>
+      <c r="H762" t="n">
+        <v>334.83</v>
+      </c>
+      <c r="I762" t="n">
+        <v>337.15</v>
+      </c>
+      <c r="J762" t="n">
+        <v>345.98</v>
+      </c>
+      <c r="K762" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:00:32+00:00</t>
+        </is>
+      </c>
+      <c r="B763" t="n">
+        <v>355.67</v>
+      </c>
+      <c r="C763" t="n">
+        <v>366.58</v>
+      </c>
+      <c r="D763" t="n">
+        <v>360.63</v>
+      </c>
+      <c r="E763" t="n">
+        <v>353.75</v>
+      </c>
+      <c r="F763" t="n">
+        <v>341.17</v>
+      </c>
+      <c r="G763" t="n">
+        <v>333.28</v>
+      </c>
+      <c r="H763" t="n">
+        <v>334.38</v>
+      </c>
+      <c r="I763" t="n">
+        <v>337.01</v>
+      </c>
+      <c r="J763" t="n">
+        <v>345.85</v>
+      </c>
+      <c r="K763" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-16 21:54:26+00:00</t>
+        </is>
+      </c>
+      <c r="B764" t="n">
+        <v>356.22</v>
+      </c>
+      <c r="C764" t="n">
+        <v>367.16</v>
+      </c>
+      <c r="D764" t="n">
+        <v>361.13</v>
+      </c>
+      <c r="E764" t="n">
+        <v>354.05</v>
+      </c>
+      <c r="F764" t="n">
+        <v>341.64</v>
+      </c>
+      <c r="G764" t="n">
+        <v>333.4</v>
+      </c>
+      <c r="H764" t="n">
+        <v>334.37</v>
+      </c>
+      <c r="I764" t="n">
+        <v>337.11</v>
+      </c>
+      <c r="J764" t="n">
+        <v>346.04</v>
+      </c>
+      <c r="K764" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-23 22:00:41+00:00</t>
+        </is>
+      </c>
+      <c r="B765" t="n">
+        <v>356.22</v>
+      </c>
+      <c r="C765" t="n">
+        <v>367.16</v>
+      </c>
+      <c r="D765" t="n">
+        <v>361.13</v>
+      </c>
+      <c r="E765" t="n">
+        <v>354.05</v>
+      </c>
+      <c r="F765" t="n">
+        <v>341.37</v>
+      </c>
+      <c r="G765" t="n">
+        <v>333.07</v>
+      </c>
+      <c r="H765" t="n">
+        <v>333.84</v>
+      </c>
+      <c r="I765" t="n">
+        <v>336.83</v>
+      </c>
+      <c r="J765" t="n">
+        <v>346.1</v>
+      </c>
+      <c r="K765" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -30022,7 +30295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B766"/>
+  <dimension ref="A1:B773"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37685,6 +37958,76 @@
       </c>
       <c r="B766" t="n">
         <v>-0.11</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B767" t="n">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>2026-08-30 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B768" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>2026-08-31 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B769" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>2026-09-08 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B770" t="n">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B771" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>2026-09-16 21:50:00+00:00</t>
+        </is>
+      </c>
+      <c r="B772" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>2026-09-23 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B773" t="n">
+        <v>-0.41</v>
       </c>
     </row>
   </sheetData>
@@ -37853,28 +38196,28 @@
         <v>0.0428</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7378199110259106</v>
+        <v>-0.7413730839606091</v>
       </c>
       <c r="J2" t="n">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="K2" t="n">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5481960944678317</v>
+        <v>0.555431642821421</v>
       </c>
       <c r="M2" t="n">
-        <v>4.114706919379015</v>
+        <v>4.091564092927637</v>
       </c>
       <c r="N2" t="n">
-        <v>25.05605347431465</v>
+        <v>24.86591912541418</v>
       </c>
       <c r="O2" t="n">
-        <v>5.005602208956945</v>
+        <v>4.986573886489017</v>
       </c>
       <c r="P2" t="n">
-        <v>377.1175665493117</v>
+        <v>377.1558241514433</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37931,28 +38274,28 @@
         <v>0.0458</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6303225940501614</v>
+        <v>-0.6325822936567048</v>
       </c>
       <c r="J3" t="n">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="K3" t="n">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4313926765267475</v>
+        <v>0.4382099634966896</v>
       </c>
       <c r="M3" t="n">
-        <v>4.263817706329132</v>
+        <v>4.233584279932627</v>
       </c>
       <c r="N3" t="n">
-        <v>29.24578695304755</v>
+        <v>28.9967153594053</v>
       </c>
       <c r="O3" t="n">
-        <v>5.407937402841083</v>
+        <v>5.384859827275479</v>
       </c>
       <c r="P3" t="n">
-        <v>384.4588501248764</v>
+        <v>384.4831760664462</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -38009,28 +38352,28 @@
         <v>0.0356</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7936635479324823</v>
+        <v>-0.7996637158412544</v>
       </c>
       <c r="J4" t="n">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="K4" t="n">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4053557074414128</v>
+        <v>0.4136811136263884</v>
       </c>
       <c r="M4" t="n">
-        <v>5.588035907345652</v>
+        <v>5.565316222772361</v>
       </c>
       <c r="N4" t="n">
-        <v>51.60499167170021</v>
+        <v>51.22782634813431</v>
       </c>
       <c r="O4" t="n">
-        <v>7.18366143910612</v>
+        <v>7.157361689067718</v>
       </c>
       <c r="P4" t="n">
-        <v>385.5288985721637</v>
+        <v>385.5935304859161</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -38087,28 +38430,28 @@
         <v>0.0368</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5539586015887661</v>
+        <v>-0.5646226800775924</v>
       </c>
       <c r="J5" t="n">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="K5" t="n">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2799407524114796</v>
+        <v>0.2906311903412654</v>
       </c>
       <c r="M5" t="n">
-        <v>5.28893268967947</v>
+        <v>5.288482360573264</v>
       </c>
       <c r="N5" t="n">
-        <v>44.08132182674814</v>
+        <v>43.98144197756043</v>
       </c>
       <c r="O5" t="n">
-        <v>6.639376614317653</v>
+        <v>6.631850569604266</v>
       </c>
       <c r="P5" t="n">
-        <v>375.2054481061157</v>
+        <v>375.3203360472475</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -38165,28 +38508,28 @@
         <v>0.0361</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4197207473827231</v>
+        <v>-0.4381520817468698</v>
       </c>
       <c r="J6" t="n">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="K6" t="n">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1902465066363729</v>
+        <v>0.2038019589842313</v>
       </c>
       <c r="M6" t="n">
-        <v>5.313069453712861</v>
+        <v>5.351915232137244</v>
       </c>
       <c r="N6" t="n">
-        <v>41.87500732244487</v>
+        <v>42.39215230395679</v>
       </c>
       <c r="O6" t="n">
-        <v>6.471090118553819</v>
+        <v>6.510925610384194</v>
       </c>
       <c r="P6" t="n">
-        <v>363.4487038384688</v>
+        <v>363.6472664548726</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -38243,28 +38586,28 @@
         <v>0.0362</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3239719357948792</v>
+        <v>-0.340741729812708</v>
       </c>
       <c r="J7" t="n">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="K7" t="n">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1148513515252665</v>
+        <v>0.1260236703154428</v>
       </c>
       <c r="M7" t="n">
-        <v>5.463440218679454</v>
+        <v>5.492533221883857</v>
       </c>
       <c r="N7" t="n">
-        <v>45.17443855851598</v>
+        <v>45.5115002366101</v>
       </c>
       <c r="O7" t="n">
-        <v>6.721193239188707</v>
+        <v>6.746221182010719</v>
       </c>
       <c r="P7" t="n">
-        <v>352.022109974291</v>
+        <v>352.2027800727824</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -38321,28 +38664,28 @@
         <v>0.036</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2400793700622976</v>
+        <v>-0.2570382426245542</v>
       </c>
       <c r="J8" t="n">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="K8" t="n">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06038229629257796</v>
+        <v>0.06898518459855063</v>
       </c>
       <c r="M8" t="n">
-        <v>5.791062117530815</v>
+        <v>5.81548884462553</v>
       </c>
       <c r="N8" t="n">
-        <v>50.08978104756266</v>
+        <v>50.39868502798418</v>
       </c>
       <c r="O8" t="n">
-        <v>7.07741344331124</v>
+        <v>7.099203126265945</v>
       </c>
       <c r="P8" t="n">
-        <v>350.8751893525933</v>
+        <v>351.0578973420227</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -38399,28 +38742,28 @@
         <v>0.0354</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2147310746671697</v>
+        <v>-0.2316540483569504</v>
       </c>
       <c r="J9" t="n">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="K9" t="n">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04796063997340183</v>
+        <v>0.05571373798488244</v>
       </c>
       <c r="M9" t="n">
-        <v>5.835622967773677</v>
+        <v>5.862786243917697</v>
       </c>
       <c r="N9" t="n">
-        <v>51.11608821240925</v>
+        <v>51.40958758901151</v>
       </c>
       <c r="O9" t="n">
-        <v>7.149551609185659</v>
+        <v>7.170047948864185</v>
       </c>
       <c r="P9" t="n">
-        <v>352.7057107751859</v>
+        <v>352.8880272994619</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -38477,28 +38820,28 @@
         <v>0.0406</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1327826133179608</v>
+        <v>-0.1452117976375513</v>
       </c>
       <c r="J10" t="n">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="K10" t="n">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0254401943221747</v>
+        <v>0.03058033608632205</v>
       </c>
       <c r="M10" t="n">
-        <v>4.88879497796062</v>
+        <v>4.903980940957452</v>
       </c>
       <c r="N10" t="n">
-        <v>37.71971272146236</v>
+        <v>37.782990722466</v>
       </c>
       <c r="O10" t="n">
-        <v>6.141637625378297</v>
+        <v>6.14678702432954</v>
       </c>
       <c r="P10" t="n">
-        <v>356.6344989701932</v>
+        <v>356.7683968036958</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -38536,7 +38879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K758"/>
+  <dimension ref="A1:K765"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81745,6 +82088,405 @@
         </is>
       </c>
     </row>
+    <row r="759">
+      <c r="A759" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-23 21:54:15+00:00</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>-40.02175358355114,176.89117521934003</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>-40.02241096373508,176.89089074482874</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>-40.02300795150999,176.89043822764611</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>-40.02360363814939,176.88998210493628</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>-40.02417274193761,176.88944798061564</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>-40.02477133568461,176.88898768516722</t>
+        </is>
+      </c>
+      <c r="H759" t="inlineStr">
+        <is>
+          <t>-40.025400009428665,176.888622469393</t>
+        </is>
+      </c>
+      <c r="I759" t="inlineStr">
+        <is>
+          <t>-40.02603331744697,176.88827267611842</t>
+        </is>
+      </c>
+      <c r="J759" t="inlineStr">
+        <is>
+          <t>-40.02668548507388,176.8879807441072</t>
+        </is>
+      </c>
+      <c r="K759" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-30 22:00:28+00:00</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>-40.02175365974898,176.89117543138013</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>-40.02240959217029,176.89088692807178</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>-40.023005856049245,176.8904323964454</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>-40.023597351722145,176.8899646112029</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>-40.024166409656175,176.8894296130322</t>
+        </is>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>-40.02476480028867,176.88896777233813</t>
+        </is>
+      </c>
+      <c r="H760" t="inlineStr">
+        <is>
+          <t>-40.02539407237333,176.88860426025224</t>
+        </is>
+      </c>
+      <c r="I760" t="inlineStr">
+        <is>
+          <t>-40.02602801271442,176.88825640627195</t>
+        </is>
+      </c>
+      <c r="J760" t="inlineStr">
+        <is>
+          <t>-40.02668176120959,176.88796932278555</t>
+        </is>
+      </c>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-31 21:54:23+00:00</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>-40.021754688419776,176.89117829392143</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>-40.022410887537035,176.89089053278667</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>-40.02300627514141,176.8904335626855</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>-40.0235971612243,176.88996408108983</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>-40.02416652010299,176.889429933397</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>-40.024764023106215,176.88896540432629</t>
+        </is>
+      </c>
+      <c r="H761" t="inlineStr">
+        <is>
+          <t>-40.02539340489356,176.88860221307093</t>
+        </is>
+      </c>
+      <c r="I761" t="inlineStr">
+        <is>
+          <t>-40.026026361572,176.88825134214804</t>
+        </is>
+      </c>
+      <c r="J761" t="inlineStr">
+        <is>
+          <t>-40.026681199116766,176.88796759881257</t>
+        </is>
+      </c>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-08 21:54:17+00:00</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>-40.02175693625568,176.89118454910454</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>-40.02241225910169,176.8908943495438</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>-40.023005856049245,176.8904323964454</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>-40.0235956372415,176.88995984018524</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>-40.02416478976974,176.88942491434858</t>
+        </is>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>-40.024761338293665,176.88895722392203</t>
+        </is>
+      </c>
+      <c r="H762" t="inlineStr">
+        <is>
+          <t>-40.02539105114876,176.88859499406342</t>
+        </is>
+      </c>
+      <c r="I762" t="inlineStr">
+        <is>
+          <t>-40.02602432399168,176.88824509280394</t>
+        </is>
+      </c>
+      <c r="J762" t="inlineStr">
+        <is>
+          <t>-40.02668046136988,176.88796533609806</t>
+        </is>
+      </c>
+      <c r="K762" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-15 22:00:32+00:00</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>-40.021758955497795,176.89119016816764</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>-40.022414887933586,176.8909016649953</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>-40.0230065799357,176.89043441086017</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>-40.02359472285173,176.88995729564257</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>-40.024162580833355,176.88941850705308</t>
+        </is>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>-40.02476010186664,176.8889534566308</t>
+        </is>
+      </c>
+      <c r="H763" t="inlineStr">
+        <is>
+          <t>-40.02538947027512,176.88859014547654</t>
+        </is>
+      </c>
+      <c r="I763" t="inlineStr">
+        <is>
+          <t>-40.026023832161904,176.8882435843416</t>
+        </is>
+      </c>
+      <c r="J763" t="inlineStr">
+        <is>
+          <t>-40.026680004669416,176.88796393537007</t>
+        </is>
+      </c>
+      <c r="K763" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-16 21:54:26+00:00</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>-40.02176105093743,176.89119599927122</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>-40.02241709767594,176.89090781421586</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>-40.02300848489995,176.89043971195179</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>-40.02359586583893,176.8899604763209</t>
+        </is>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>-40.02416431116689,176.88942352610118</t>
+        </is>
+      </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>-40.0247605257845,176.88895474827348</t>
+        </is>
+      </c>
+      <c r="H764" t="inlineStr">
+        <is>
+          <t>-40.02538943514461,176.88859003773018</t>
+        </is>
+      </c>
+      <c r="I764" t="inlineStr">
+        <is>
+          <t>-40.0260241834689,176.88824466181472</t>
+        </is>
+      </c>
+      <c r="J764" t="inlineStr">
+        <is>
+          <t>-40.02668067215471,176.8879659825879</t>
+        </is>
+      </c>
+      <c r="K764" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-23 22:00:41+00:00</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>-40.02176105093743,176.89119599927122</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>-40.02241709767594,176.89090781421586</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>-40.02300848489995,176.89043971195179</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>-40.02359586583893,176.8899604763209</t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>-40.02416331714552,176.88942064281824</t>
+        </is>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>-40.024759360010364,176.8889511962561</t>
+        </is>
+      </c>
+      <c r="H765" t="inlineStr">
+        <is>
+          <t>-40.02538757322649,176.88858432717257</t>
+        </is>
+      </c>
+      <c r="I765" t="inlineStr">
+        <is>
+          <t>-40.02602319980929,176.88824164489012</t>
+        </is>
+      </c>
+      <c r="J765" t="inlineStr">
+        <is>
+          <t>-40.02668088293955,176.88796662907777</t>
+        </is>
+      </c>
+      <c r="K765" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
